--- a/output/topology_excel/8302.xlsx
+++ b/output/topology_excel/8302.xlsx
@@ -425,58 +425,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>房间1</t>
+          <t>RoomA</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>类型1</t>
+          <t>RoomB</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>面积1</t>
+          <t>ConnectionType</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>房间2</t>
+          <t>Count</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>类型2</t>
+          <t>Length</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>面积2</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>连接类型</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>length</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>width</t>
+          <t>Width</t>
         </is>
       </c>
     </row>
@@ -484,37 +464,21 @@
       <c r="A2" t="n">
         <v>2</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>24125</v>
+      <c r="B2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>62</v>
       </c>
       <c r="F2" t="n">
-        <v>63518</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>门</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>62</v>
-      </c>
-      <c r="J2" t="n">
         <v>13</v>
       </c>
     </row>
@@ -522,37 +486,21 @@
       <c r="A3" t="n">
         <v>3</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>171560</v>
+      <c r="B3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>69</v>
       </c>
       <c r="F3" t="n">
-        <v>63518</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>门</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>69</v>
-      </c>
-      <c r="J3" t="n">
         <v>13</v>
       </c>
     </row>
@@ -560,37 +508,21 @@
       <c r="A4" t="n">
         <v>1</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>145848</v>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>88</v>
       </c>
       <c r="F4" t="n">
-        <v>63518</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>门</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>88</v>
-      </c>
-      <c r="J4" t="n">
         <v>13</v>
       </c>
     </row>
@@ -598,37 +530,21 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>63518</v>
+      <c r="B5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>76</v>
       </c>
       <c r="F5" t="n">
-        <v>105792</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>门</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>76</v>
-      </c>
-      <c r="J5" t="n">
         <v>13</v>
       </c>
     </row>
@@ -636,37 +552,21 @@
       <c r="A6" t="n">
         <v>4</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>63518</v>
+      <c r="B6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>50</v>
       </c>
       <c r="F6" t="n">
-        <v>16594</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>门</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>50</v>
-      </c>
-      <c r="J6" t="n">
         <v>13</v>
       </c>
     </row>
@@ -674,37 +574,21 @@
       <c r="A7" t="n">
         <v>1</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>145848</v>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>193</v>
       </c>
       <c r="F7" t="n">
-        <v>24125</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>193</v>
-      </c>
-      <c r="J7" t="n">
         <v>12</v>
       </c>
     </row>
@@ -712,37 +596,21 @@
       <c r="A8" t="n">
         <v>1</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>145848</v>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>141</v>
       </c>
       <c r="F8" t="n">
-        <v>63518</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>141</v>
-      </c>
-      <c r="J8" t="n">
         <v>60</v>
       </c>
     </row>
@@ -750,37 +618,21 @@
       <c r="A9" t="n">
         <v>1</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>145848</v>
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>402</v>
       </c>
       <c r="F9" t="n">
-        <v>105792</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>402</v>
-      </c>
-      <c r="J9" t="n">
         <v>12</v>
       </c>
     </row>
@@ -788,37 +640,21 @@
       <c r="A10" t="n">
         <v>2</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>24125</v>
+      <c r="B10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>206</v>
       </c>
       <c r="F10" t="n">
-        <v>171560</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>206</v>
-      </c>
-      <c r="J10" t="n">
         <v>35</v>
       </c>
     </row>
@@ -826,37 +662,21 @@
       <c r="A11" t="n">
         <v>2</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>24125</v>
+      <c r="B11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>90</v>
       </c>
       <c r="F11" t="n">
-        <v>63518</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>90</v>
-      </c>
-      <c r="J11" t="n">
         <v>13</v>
       </c>
     </row>
@@ -864,37 +684,21 @@
       <c r="A12" t="n">
         <v>3</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>171560</v>
+      <c r="B12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>110</v>
       </c>
       <c r="F12" t="n">
-        <v>63518</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" t="n">
-        <v>110</v>
-      </c>
-      <c r="J12" t="n">
         <v>23</v>
       </c>
     </row>
@@ -902,37 +706,21 @@
       <c r="A13" t="n">
         <v>4</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>63518</v>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>164</v>
       </c>
       <c r="F13" t="n">
-        <v>105792</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" t="n">
-        <v>164</v>
-      </c>
-      <c r="J13" t="n">
         <v>13</v>
       </c>
     </row>
@@ -940,37 +728,21 @@
       <c r="A14" t="n">
         <v>4</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>63518</v>
+      <c r="B14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>68</v>
       </c>
       <c r="F14" t="n">
-        <v>16594</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" t="n">
-        <v>68</v>
-      </c>
-      <c r="J14" t="n">
         <v>13</v>
       </c>
     </row>
@@ -978,37 +750,21 @@
       <c r="A15" t="n">
         <v>5</v>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>105792</v>
+      <c r="B15" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>151</v>
       </c>
       <c r="F15" t="n">
-        <v>16594</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" t="n">
-        <v>151</v>
-      </c>
-      <c r="J15" t="n">
         <v>138</v>
       </c>
     </row>

--- a/output/topology_excel/8302.xlsx
+++ b/output/topology_excel/8302.xlsx
@@ -465,7 +465,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -487,7 +487,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="n">
         <v>4</v>
-      </c>
-      <c r="B6" t="n">
-        <v>6</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -575,7 +575,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>193</v>
+        <v>402</v>
       </c>
       <c r="F7" t="n">
         <v>12</v>
@@ -597,7 +597,7 @@
         <v>1</v>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -608,10 +608,10 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="F8" t="n">
-        <v>60</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -619,7 +619,7 @@
         <v>1</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -630,10 +630,10 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>402</v>
+        <v>151</v>
       </c>
       <c r="F9" t="n">
-        <v>12</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10">
@@ -641,7 +641,7 @@
         <v>2</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -652,10 +652,10 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="F10" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -663,7 +663,7 @@
         <v>2</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -674,18 +674,18 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>90</v>
+        <v>206</v>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -696,15 +696,15 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="F12" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B13" t="n">
         <v>5</v>
@@ -718,15 +718,15 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>164</v>
+        <v>141</v>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B14" t="n">
         <v>6</v>
@@ -740,18 +740,18 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>68</v>
+        <v>110</v>
       </c>
       <c r="F14" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -762,10 +762,10 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>151</v>
+        <v>68</v>
       </c>
       <c r="F15" t="n">
-        <v>138</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/8302.xlsx
+++ b/output/topology_excel/8302.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
         </is>
       </c>
     </row>
@@ -481,6 +491,8 @@
       <c r="F2" t="n">
         <v>13</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +515,8 @@
       <c r="F3" t="n">
         <v>13</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +539,8 @@
       <c r="F4" t="n">
         <v>13</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +563,8 @@
       <c r="F5" t="n">
         <v>13</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +587,8 @@
       <c r="F6" t="n">
         <v>13</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +611,8 @@
       <c r="F7" t="n">
         <v>12</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -613,6 +635,8 @@
       <c r="F8" t="n">
         <v>13</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -627,13 +651,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>151</v>
+        <v>125</v>
       </c>
       <c r="F9" t="n">
-        <v>138</v>
+        <v>12</v>
+      </c>
+      <c r="G9" t="n">
+        <v>139</v>
+      </c>
+      <c r="H9" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="10">
@@ -657,6 +687,8 @@
       <c r="F10" t="n">
         <v>12</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -671,13 +703,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="F11" t="n">
-        <v>35</v>
+        <v>13</v>
+      </c>
+      <c r="G11" t="n">
+        <v>22</v>
+      </c>
+      <c r="H11" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="12">
@@ -701,6 +739,8 @@
       <c r="F12" t="n">
         <v>13</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -715,13 +755,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>141</v>
+        <v>47</v>
       </c>
       <c r="F13" t="n">
-        <v>60</v>
+        <v>13</v>
+      </c>
+      <c r="G13" t="n">
+        <v>128</v>
+      </c>
+      <c r="H13" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="14">
@@ -737,13 +783,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="F14" t="n">
-        <v>23</v>
+        <v>13</v>
+      </c>
+      <c r="G14" t="n">
+        <v>13</v>
+      </c>
+      <c r="H14" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -767,6 +819,8 @@
       <c r="F15" t="n">
         <v>13</v>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
